--- a/Pruebas calificadas/COLEGIO JOSE MARIA CARBONELL CURSO 1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JOSE MARIA CARBONELL CURSO 1102_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1253,11 +1245,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -1265,7 +1253,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1506,11 +1494,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -1518,7 +1502,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1759,11 +1743,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -1771,7 +1751,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2012,11 +1992,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -2024,7 +2000,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2265,11 +2241,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -2277,7 +2249,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2518,11 +2490,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -2530,7 +2498,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2771,11 +2739,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -2783,7 +2747,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3024,11 +2988,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -3036,7 +2996,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3277,11 +3237,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -3289,7 +3245,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3530,11 +3486,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -3542,7 +3494,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3783,11 +3735,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -3795,7 +3743,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4036,11 +3984,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -4048,7 +3992,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4289,11 +4233,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -4301,7 +4241,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4542,11 +4482,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -4554,7 +4490,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4795,11 +4731,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -4807,7 +4739,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5048,11 +4980,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -5060,7 +4988,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5301,11 +5229,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -5313,7 +5237,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5554,11 +5478,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -5566,7 +5486,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5807,11 +5727,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -5819,7 +5735,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6060,11 +5976,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -6072,7 +5984,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6313,11 +6225,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -6325,7 +6233,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6566,11 +6474,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -6578,7 +6482,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6819,11 +6723,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -6831,7 +6731,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7020,11 +6920,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -7032,7 +6928,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7273,11 +7169,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -7285,7 +7177,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7526,11 +7418,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -7538,7 +7426,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7779,11 +7667,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -7791,7 +7675,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8032,11 +7916,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -8044,7 +7924,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8285,11 +8165,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -8297,7 +8173,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8538,11 +8414,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -8550,7 +8422,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8791,11 +8663,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -8803,7 +8671,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9044,11 +8912,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001018252</t>
@@ -9056,7 +8920,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JOSE MARIA CARBONELL (IED)</t>
+          <t>COLEGIO JOSE MARIA CARBONELL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
